--- a/data/trans_dic/P55$familiar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 74,42</t>
+          <t>11,43; 80,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 75,31</t>
+          <t>16,9; 69,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,41; 82,31</t>
+          <t>27,19; 82,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,16; 78,83</t>
+          <t>48,77; 77,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,36</t>
+          <t>0,0; 54,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,32; 70,97</t>
+          <t>35,97; 73,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 68,61</t>
+          <t>23,62; 68,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,38; 89,48</t>
+          <t>70,37; 89,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 54,71</t>
+          <t>9,83; 53,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,31; 66,99</t>
+          <t>35,79; 66,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,0; 68,71</t>
+          <t>30,51; 67,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,39; 81,21</t>
+          <t>63,38; 81,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 56,99</t>
+          <t>6,66; 59,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,12</t>
+          <t>0,0; 26,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 52,93</t>
+          <t>6,53; 48,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,56; 78,02</t>
+          <t>33,49; 77,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 61,18</t>
+          <t>18,77; 61,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 33,07</t>
+          <t>7,72; 31,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,87; 47,69</t>
+          <t>14,0; 48,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,31; 71,89</t>
+          <t>52,07; 71,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,51; 50,55</t>
+          <t>19,86; 51,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 22,99</t>
+          <t>6,16; 23,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 41,9</t>
+          <t>14,62; 41,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,3; 70,24</t>
+          <t>50,72; 70,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,06</t>
+          <t>0,0; 44,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,35</t>
+          <t>0,0; 38,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 52,06</t>
+          <t>10,1; 49,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,46; 66,15</t>
+          <t>36,89; 66,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 48,54</t>
+          <t>18,38; 51,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 55,64</t>
+          <t>19,51; 55,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,42</t>
+          <t>0,0; 38,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,31; 65,37</t>
+          <t>45,18; 65,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 45,02</t>
+          <t>16,04; 44,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 41,03</t>
+          <t>12,8; 40,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 36,42</t>
+          <t>8,55; 37,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 62,38</t>
+          <t>45,19; 62,5</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,9</t>
+          <t>0,0; 28,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 72,58</t>
+          <t>27,95; 72,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 52,96</t>
+          <t>11,15; 58,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,07; 71,22</t>
+          <t>32,76; 69,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 37,17</t>
+          <t>6,82; 35,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,89; 57,46</t>
+          <t>27,37; 58,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 60,7</t>
+          <t>20,35; 60,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,22; 70,65</t>
+          <t>51,39; 71,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 29,47</t>
+          <t>6,84; 28,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,68; 57,16</t>
+          <t>30,91; 58,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,49; 52,92</t>
+          <t>21,3; 52,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,81; 66,9</t>
+          <t>48,72; 67,09</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,35</t>
+          <t>0,0; 55,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 83,54</t>
+          <t>15,71; 83,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 56,37</t>
+          <t>12,01; 56,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 53,41</t>
+          <t>11,67; 58,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 42,15</t>
+          <t>8,17; 41,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 41,48</t>
+          <t>7,69; 41,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,18; 68,73</t>
+          <t>40,0; 69,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 44,61</t>
+          <t>8,92; 44,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 41,33</t>
+          <t>12,41; 41,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 45,79</t>
+          <t>12,56; 45,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,88; 58,63</t>
+          <t>35,05; 60,63</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 41,74</t>
+          <t>5,25; 46,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 41,38</t>
+          <t>5,84; 41,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,35; 56,97</t>
+          <t>16,91; 57,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,66; 56,37</t>
+          <t>31,54; 56,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,37; 56,51</t>
+          <t>17,33; 55,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,97; 50,13</t>
+          <t>9,97; 49,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,81</t>
+          <t>0,0; 29,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,84; 66,03</t>
+          <t>45,54; 66,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 44,75</t>
+          <t>16,62; 44,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,33; 40,35</t>
+          <t>13,09; 37,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,44; 32,97</t>
+          <t>8,84; 33,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,97; 57,92</t>
+          <t>43,0; 59,2</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,73</t>
+          <t>0,0; 27,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 37,67</t>
+          <t>6,81; 35,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 39,28</t>
+          <t>7,16; 39,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,39; 69,82</t>
+          <t>33,35; 69,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,08; 33,15</t>
+          <t>5,94; 31,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 44,06</t>
+          <t>17,04; 43,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 37,47</t>
+          <t>12,81; 37,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,2; 59,49</t>
+          <t>37,72; 59,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 24,12</t>
+          <t>5,53; 24,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,46; 35,71</t>
+          <t>15,28; 33,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,28; 33,24</t>
+          <t>13,05; 32,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,67; 59,66</t>
+          <t>41,21; 60,37</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 37,94</t>
+          <t>11,43; 39,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,53; 51,77</t>
+          <t>10,22; 52,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,44; 50,56</t>
+          <t>13,93; 51,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,72; 63,54</t>
+          <t>27,45; 65,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,86; 35,34</t>
+          <t>10,36; 35,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,15; 46,22</t>
+          <t>19,54; 48,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 47,08</t>
+          <t>17,07; 47,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,62; 63,52</t>
+          <t>43,61; 63,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 32,58</t>
+          <t>13,39; 31,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,78; 42,69</t>
+          <t>18,64; 41,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 45,0</t>
+          <t>21,13; 44,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,64; 60,67</t>
+          <t>42,9; 59,79</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,41</t>
+          <t>13,87; 28,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,96</t>
+          <t>16,53; 31,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,51; 37,22</t>
+          <t>21,89; 36,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45,24; 57,42</t>
+          <t>44,77; 57,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,56; 31,66</t>
+          <t>19,92; 31,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,68; 37,75</t>
+          <t>26,5; 37,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,57</t>
+          <t>22,36; 34,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55,09; 62,54</t>
+          <t>54,41; 62,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,96</t>
+          <t>19,05; 28,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,36; 33,38</t>
+          <t>24,47; 33,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,68</t>
+          <t>23,37; 33,24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52,86; 59,54</t>
+          <t>52,79; 59,39</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>983; 6451</t>
+          <t>991; 6990</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1977; 8871</t>
+          <t>1991; 8147</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2466; 7407</t>
+          <t>2447; 7416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13289; 21310</t>
+          <t>13184; 21084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5465</t>
+          <t>0; 5568</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10328; 20181</t>
+          <t>10230; 20965</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6140; 16990</t>
+          <t>5848; 17051</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22825; 29436</t>
+          <t>23149; 29276</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1965; 10346</t>
+          <t>1859; 10204</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14200; 26941</t>
+          <t>14393; 26912</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10468; 23196</t>
+          <t>10300; 22929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38590; 48670</t>
+          <t>37982; 48574</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1745; 9278</t>
+          <t>1084; 9664</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4732</t>
+          <t>0; 6320</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>839; 6740</t>
+          <t>831; 6239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5008; 12003</t>
+          <t>5152; 11957</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4646; 13894</t>
+          <t>4262; 13977</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3251; 14002</t>
+          <t>3268; 13443</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5041; 17333</t>
+          <t>5090; 17454</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28771; 39543</t>
+          <t>28642; 39422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7606; 19710</t>
+          <t>7744; 19907</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3603; 15141</t>
+          <t>4056; 15716</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7471; 20563</t>
+          <t>7174; 20587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36106; 49442</t>
+          <t>35698; 49291</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4799</t>
+          <t>0; 4684</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1514; 7671</t>
+          <t>1488; 7290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9106; 16987</t>
+          <t>9475; 17130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6560; 17351</t>
+          <t>6569; 18249</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4635; 14741</t>
+          <t>5169; 14783</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7524</t>
+          <t>0; 6664</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19731; 29110</t>
+          <t>20119; 29064</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8341; 20782</t>
+          <t>7407; 20386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5396; 16779</t>
+          <t>5232; 16537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2706; 11677</t>
+          <t>2741; 11894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31459; 43798</t>
+          <t>31729; 43888</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3736</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5147; 13981</t>
+          <t>5384; 13971</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1490; 7392</t>
+          <t>1556; 8153</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5471; 11784</t>
+          <t>5420; 11580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2227; 11863</t>
+          <t>2177; 11247</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11008; 22678</t>
+          <t>10804; 23000</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5846; 17834</t>
+          <t>5978; 17804</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18400; 25377</t>
+          <t>18459; 25719</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3165; 13351</t>
+          <t>3099; 13039</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18016; 33571</t>
+          <t>18151; 34188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9314; 22934</t>
+          <t>9233; 22640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25606; 35098</t>
+          <t>25561; 35197</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4809</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>785; 4120</t>
+          <t>775; 4120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>963; 4506</t>
+          <t>960; 4528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1127; 8342</t>
+          <t>1823; 9207</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2072; 10648</t>
+          <t>2063; 10543</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1846; 10021</t>
+          <t>1857; 10052</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6483; 11091</t>
+          <t>6455; 11244</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2182; 10821</t>
+          <t>2165; 10803</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4263; 14148</t>
+          <t>4249; 14099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3719; 13322</t>
+          <t>3653; 13279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8416; 14148</t>
+          <t>8459; 14631</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>945; 7501</t>
+          <t>944; 8315</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1055; 7483</t>
+          <t>1055; 7519</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2442; 8509</t>
+          <t>2525; 8541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7417; 13636</t>
+          <t>7629; 13567</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4857; 15797</t>
+          <t>4843; 15434</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2122; 10669</t>
+          <t>2121; 10587</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7206</t>
+          <t>0; 6811</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14154; 20845</t>
+          <t>14375; 21050</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7759; 20552</t>
+          <t>7632; 20416</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5248; 15882</t>
+          <t>5151; 14858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3236; 12637</t>
+          <t>3390; 13000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23401; 32293</t>
+          <t>23977; 33007</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4066</t>
+          <t>0; 5186</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1977; 11047</t>
+          <t>1998; 10278</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1831; 10381</t>
+          <t>1893; 10416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7760; 16229</t>
+          <t>7753; 16264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3165; 12987</t>
+          <t>2328; 12261</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8628; 21750</t>
+          <t>8411; 21490</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6941; 21107</t>
+          <t>7216; 21252</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20945; 31788</t>
+          <t>20156; 31770</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3271; 13961</t>
+          <t>3200; 14364</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12163; 28103</t>
+          <t>12027; 26751</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11819; 27507</t>
+          <t>10795; 26713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31953; 45748</t>
+          <t>31598; 46295</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2996; 12330</t>
+          <t>3714; 12801</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2193; 10782</t>
+          <t>2128; 10829</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3572; 12506</t>
+          <t>3446; 12839</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4372; 10802</t>
+          <t>4667; 11063</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4691; 16809</t>
+          <t>4926; 16759</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8981; 21674</t>
+          <t>9163; 22594</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10602; 26213</t>
+          <t>9504; 26694</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25629; 37324</t>
+          <t>25621; 37189</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9957; 26086</t>
+          <t>10719; 25505</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13393; 28910</t>
+          <t>12625; 27771</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17167; 36180</t>
+          <t>16989; 35945</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>33058; 45961</t>
+          <t>32501; 45293</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>16410; 33428</t>
+          <t>17560; 35546</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24227; 45248</t>
+          <t>24159; 46071</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26123; 45209</t>
+          <t>26582; 44854</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71058; 90192</t>
+          <t>70318; 89567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>45180; 73115</t>
+          <t>45999; 73873</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74576; 105523</t>
+          <t>74063; 105453</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58493; 92435</t>
+          <t>59795; 92871</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>180821; 205271</t>
+          <t>178607; 204104</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>67956; 99972</t>
+          <t>68120; 100743</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103687; 142104</t>
+          <t>104150; 142057</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93890; 130956</t>
+          <t>90859; 129260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>256524; 288971</t>
+          <t>256200; 288244</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 80,63</t>
+          <t>11,28; 75,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,9; 69,16</t>
+          <t>17,02; 75,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,19; 82,41</t>
+          <t>27,51; 82,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,77; 77,99</t>
+          <t>42,07; 70,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,36</t>
+          <t>0,0; 55,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 73,73</t>
+          <t>35,33; 73,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 68,85</t>
+          <t>24,29; 67,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70,37; 89,0</t>
+          <t>68,48; 87,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 53,96</t>
+          <t>11,79; 58,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,79; 66,92</t>
+          <t>35,58; 66,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,51; 67,91</t>
+          <t>31,05; 67,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,38; 81,05</t>
+          <t>59,88; 78,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 59,36</t>
+          <t>10,34; 55,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,87</t>
+          <t>0,0; 23,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 48,99</t>
+          <t>6,59; 48,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,49; 77,72</t>
+          <t>32,22; 77,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 61,55</t>
+          <t>21,36; 62,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 31,76</t>
+          <t>7,58; 32,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 48,02</t>
+          <t>13,89; 47,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,07; 71,67</t>
+          <t>52,25; 72,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,86; 51,06</t>
+          <t>22,08; 52,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 23,87</t>
+          <t>6,03; 22,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,62; 41,95</t>
+          <t>15,38; 42,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,72; 70,03</t>
+          <t>51,14; 69,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,96</t>
+          <t>0,0; 53,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,25</t>
+          <t>0,0; 39,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 49,47</t>
+          <t>10,52; 52,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,89; 66,7</t>
+          <t>34,76; 66,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 51,05</t>
+          <t>18,82; 49,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 55,8</t>
+          <t>19,43; 56,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,46</t>
+          <t>0,0; 44,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45,18; 65,26</t>
+          <t>44,75; 65,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 44,16</t>
+          <t>16,03; 44,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 40,44</t>
+          <t>12,77; 42,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 37,09</t>
+          <t>7,29; 38,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,19; 62,5</t>
+          <t>45,22; 62,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,31</t>
+          <t>0,0; 28,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,95; 72,53</t>
+          <t>27,76; 72,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 58,41</t>
+          <t>11,14; 58,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 69,99</t>
+          <t>31,38; 68,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 35,23</t>
+          <t>6,95; 36,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 58,28</t>
+          <t>26,92; 59,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,35; 60,6</t>
+          <t>20,64; 60,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,39; 71,6</t>
+          <t>51,11; 71,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 28,78</t>
+          <t>7,32; 30,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 58,21</t>
+          <t>32,35; 59,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 52,24</t>
+          <t>22,63; 52,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,72; 67,09</t>
+          <t>49,63; 67,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,67</t>
+          <t>0,0; 57,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 74,44</t>
+          <t>11,52; 74,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 83,54</t>
+          <t>15,91; 83,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 56,65</t>
+          <t>12,0; 56,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 58,95</t>
+          <t>7,15; 54,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 41,74</t>
+          <t>8,24; 38,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 41,61</t>
+          <t>7,56; 39,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,0; 69,68</t>
+          <t>40,79; 71,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 44,54</t>
+          <t>10,11; 44,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 41,18</t>
+          <t>12,15; 44,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 45,65</t>
+          <t>12,4; 43,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,05; 60,63</t>
+          <t>35,45; 60,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 46,27</t>
+          <t>5,28; 42,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 41,59</t>
+          <t>5,81; 41,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 57,19</t>
+          <t>12,22; 58,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,54; 56,09</t>
+          <t>32,01; 56,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,33; 55,21</t>
+          <t>16,84; 53,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,97; 49,75</t>
+          <t>14,22; 50,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,12</t>
+          <t>0,0; 29,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,54; 66,68</t>
+          <t>45,29; 67,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,62; 44,46</t>
+          <t>16,64; 44,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,09; 37,75</t>
+          <t>13,14; 37,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 33,92</t>
+          <t>9,47; 33,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,0; 59,2</t>
+          <t>43,08; 60,13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,71</t>
+          <t>0,0; 22,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 35,05</t>
+          <t>6,56; 35,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 39,41</t>
+          <t>7,08; 37,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,35; 69,97</t>
+          <t>36,14; 70,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 31,3</t>
+          <t>6,41; 32,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 43,53</t>
+          <t>16,13; 43,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,81; 37,73</t>
+          <t>12,72; 38,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,72; 59,45</t>
+          <t>36,57; 56,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 24,81</t>
+          <t>5,75; 24,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,28; 33,99</t>
+          <t>15,04; 34,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 32,28</t>
+          <t>14,29; 32,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,21; 60,37</t>
+          <t>39,41; 56,93</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,43; 39,39</t>
+          <t>10,57; 37,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 52,0</t>
+          <t>10,01; 51,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,93; 51,9</t>
+          <t>15,87; 51,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,45; 65,07</t>
+          <t>26,26; 64,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,36; 35,24</t>
+          <t>10,04; 34,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,54; 48,18</t>
+          <t>19,03; 46,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,07; 47,95</t>
+          <t>19,84; 46,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,61; 63,29</t>
+          <t>44,28; 63,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 31,86</t>
+          <t>12,78; 31,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 41,01</t>
+          <t>19,52; 42,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,13; 44,7</t>
+          <t>20,56; 44,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,9; 59,79</t>
+          <t>43,0; 59,65</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,08</t>
+          <t>13,68; 27,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,52</t>
+          <t>16,22; 31,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,93</t>
+          <t>21,9; 36,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44,77; 57,02</t>
+          <t>43,59; 55,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,99</t>
+          <t>19,9; 31,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,5; 37,72</t>
+          <t>26,4; 37,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,36; 34,74</t>
+          <t>22,32; 34,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54,41; 62,18</t>
+          <t>53,59; 61,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,18</t>
+          <t>19,27; 28,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24,47; 33,37</t>
+          <t>24,25; 33,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,24</t>
+          <t>23,35; 33,03</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,39</t>
+          <t>51,54; 58,16</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26751</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>43611</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>991; 6990</t>
+          <t>978; 6577</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1991; 8147</t>
+          <t>2005; 8870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2447; 7416</t>
+          <t>2475; 7410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13184; 21084</t>
+          <t>12300; 20678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5568</t>
+          <t>0; 5653</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10230; 20965</t>
+          <t>10047; 20909</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5848; 17051</t>
+          <t>6016; 16797</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23149; 29276</t>
+          <t>23000; 29385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1859; 10204</t>
+          <t>2229; 11123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14393; 26912</t>
+          <t>14309; 26636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10300; 22929</t>
+          <t>10483; 22846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37982; 48574</t>
+          <t>37616; 49246</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>45239</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1084; 9664</t>
+          <t>1684; 9045</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6320</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>831; 6239</t>
+          <t>839; 6201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5152; 11957</t>
+          <t>5306; 12775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4262; 13977</t>
+          <t>4850; 14205</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3268; 13443</t>
+          <t>3210; 13556</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5090; 17454</t>
+          <t>5048; 17408</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28642; 39422</t>
+          <t>30583; 42207</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7744; 19907</t>
+          <t>8609; 20483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4056; 15716</t>
+          <t>3972; 15080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7174; 20587</t>
+          <t>7546; 20902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35698; 49291</t>
+          <t>38353; 52151</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>37342</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4684</t>
+          <t>0; 5549</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 5620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1488; 7290</t>
+          <t>1551; 7708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9475; 17130</t>
+          <t>8765; 16873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6569; 18249</t>
+          <t>6726; 17836</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5169; 14783</t>
+          <t>5146; 14855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6664</t>
+          <t>0; 7670</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20119; 29064</t>
+          <t>19960; 29172</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7407; 20386</t>
+          <t>7400; 20492</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5232; 16537</t>
+          <t>5221; 17343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2741; 11894</t>
+          <t>2339; 12203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31729; 43888</t>
+          <t>31574; 43576</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30685</t>
+          <t>32336</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3791</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5384; 13971</t>
+          <t>5347; 13952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1556; 8153</t>
+          <t>1555; 8124</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5420; 11580</t>
+          <t>5573; 12206</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2177; 11247</t>
+          <t>2218; 11734</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10804; 23000</t>
+          <t>10623; 23520</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5978; 17804</t>
+          <t>6063; 17894</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18459; 25719</t>
+          <t>19417; 27080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3099; 13039</t>
+          <t>3318; 13857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18151; 34188</t>
+          <t>18997; 34765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9233; 22640</t>
+          <t>9808; 22903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25561; 35197</t>
+          <t>27669; 37814</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>12017</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4809</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1023; 6681</t>
+          <t>1034; 6684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>775; 4120</t>
+          <t>785; 4118</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>960; 4528</t>
+          <t>984; 4620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1823; 9207</t>
+          <t>1117; 8560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2063; 10543</t>
+          <t>2083; 9729</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1857; 10052</t>
+          <t>1827; 9536</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6455; 11244</t>
+          <t>6854; 11940</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2165; 10803</t>
+          <t>2451; 10722</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4249; 14099</t>
+          <t>4160; 15075</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3653; 13279</t>
+          <t>3609; 12697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8459; 14631</t>
+          <t>8863; 15111</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>28431</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>944; 8315</t>
+          <t>948; 7548</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1055; 7519</t>
+          <t>1050; 7460</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2525; 8541</t>
+          <t>1824; 8677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7629; 13567</t>
+          <t>7755; 13791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4843; 15434</t>
+          <t>4706; 15033</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2121; 10587</t>
+          <t>3026; 10650</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6811</t>
+          <t>0; 6861</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14375; 21050</t>
+          <t>14561; 21542</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7632; 20416</t>
+          <t>7643; 20296</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5151; 14858</t>
+          <t>5174; 14929</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3390; 13000</t>
+          <t>3629; 12863</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23977; 33007</t>
+          <t>24288; 33895</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>45559</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5186</t>
+          <t>0; 4277</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1998; 10278</t>
+          <t>1924; 10361</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1893; 10416</t>
+          <t>1871; 9814</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7753; 16264</t>
+          <t>10332; 20244</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2328; 12261</t>
+          <t>2510; 12721</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8411; 21490</t>
+          <t>7962; 21255</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7216; 21252</t>
+          <t>7163; 21595</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20156; 31770</t>
+          <t>23872; 36672</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3200; 14364</t>
+          <t>3331; 14093</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12027; 26751</t>
+          <t>11832; 27068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10795; 26713</t>
+          <t>11829; 27094</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31598; 46295</t>
+          <t>36992; 53440</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>36922</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>45459</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3714; 12801</t>
+          <t>3434; 12310</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2128; 10829</t>
+          <t>2084; 10772</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3446; 12839</t>
+          <t>3925; 12633</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4667; 11063</t>
+          <t>5100; 12492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4926; 16759</t>
+          <t>4777; 16231</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9163; 22594</t>
+          <t>8922; 21592</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9504; 26694</t>
+          <t>11045; 26140</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25621; 37189</t>
+          <t>30246; 43534</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10719; 25505</t>
+          <t>10228; 25052</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12625; 27771</t>
+          <t>13217; 29091</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16989; 35945</t>
+          <t>16532; 35886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32501; 45293</t>
+          <t>37724; 52331</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>192209</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>272302</t>
+          <t>289993</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17560; 35546</t>
+          <t>17321; 35325</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24159; 46071</t>
+          <t>23707; 45501</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26582; 44854</t>
+          <t>26604; 44783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70318; 89567</t>
+          <t>73721; 94448</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>45999; 73873</t>
+          <t>45953; 73648</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74063; 105453</t>
+          <t>73799; 105405</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59795; 92871</t>
+          <t>59683; 92419</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>178607; 204104</t>
+          <t>191431; 218341</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>68120; 100743</t>
+          <t>68901; 101870</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>104150; 142057</t>
+          <t>103211; 142669</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90859; 129260</t>
+          <t>90803; 128435</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>256200; 288244</t>
+          <t>271305; 306124</t>
         </is>
       </c>
     </row>
